--- a/MainTop/20.08.2026 Имена Москва/print.xlsx
+++ b/MainTop/20.08.2026 Имена Москва/print.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\20.08.2026 Имена Москва\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\20.08.2026 Имена Москва\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FE635C-1D5B-4089-8CF7-4162077CDD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222FCE56-0AF8-411B-9125-519DB9C31970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -517,7 +517,7 @@
   <dimension ref="A1:B37"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="21" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
